--- a/xslx/grille_correction_travail_session_containers.xlsx
+++ b/xslx/grille_correction_travail_session_containers.xlsx
@@ -1,470 +1,78 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Export Summary" sheetId="1" r:id="rId5"/>
-    <sheet name="Correction" sheetId="2" r:id="rId6"/>
-    <sheet name="Référentiel" sheetId="3" r:id="rId7"/>
-    <sheet name="Consignes" sheetId="4" r:id="rId8"/>
+    <sheet name="Export Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Correction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Référentiel" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Consignes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames/>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Perplexity</author>
-  </authors>
-  <commentList>
-    <comment ref="C6" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-          </rPr>
-          <t>Perplexity:
-Entrer une note de 0 à 5.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C7" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-          </rPr>
-          <t>Perplexity:
-Entrer une note de 0 à 5.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-          </rPr>
-          <t>Perplexity:
-Entrer une note de 0 à 4.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-          </rPr>
-          <t>Perplexity:
-Entrer une note de 0 à 4.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C10" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-          </rPr>
-          <t>Perplexity:
-Entrer une note de 0 à 5.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-          </rPr>
-          <t>Perplexity:
-Entrer une note de 0 à 4.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C12" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-          </rPr>
-          <t>Perplexity:
-Entrer une note de 0 à 4.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-          </rPr>
-          <t>Perplexity:
-Entrer une note de 0 à 4.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C14" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-          </rPr>
-          <t>Perplexity:
-Entrer une note de 0 à 2.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-          </rPr>
-          <t>Perplexity:
-Entrer une note de 0 à 2.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-          </rPr>
-          <t>Perplexity:
-Entrer une note de 0 à 5.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="71">
-  <si>
-    <t>This document was exported from Numbers.  Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
-  </si>
-  <si>
-    <t>Numbers Sheet Name</t>
-  </si>
-  <si>
-    <t>Numbers Table Name</t>
-  </si>
-  <si>
-    <t>Excel Worksheet Name</t>
-  </si>
-  <si>
-    <t>Correction</t>
-  </si>
-  <si>
-    <t>Table 1</t>
-  </si>
-  <si>
-    <t>Grille de correction — plateforme pédagogique conteneurisée</t>
-  </si>
-  <si>
-    <t>Équipe</t>
-  </si>
-  <si>
-    <t>Correcteur</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Critère</t>
-  </si>
-  <si>
-    <t>Maximum</t>
-  </si>
-  <si>
-    <t>Note attribuée</t>
-  </si>
-  <si>
-    <t>Niveau</t>
-  </si>
-  <si>
-    <t>Commentaires / preuves observées</t>
-  </si>
-  <si>
-    <t>Indicateurs clés</t>
-  </si>
-  <si>
-    <t>VM as Code avec cloud-init</t>
-  </si>
-  <si>
-    <t>Présence d’un vrai fichier cloud-init; automatisation de l’utilisateur, SSH, mises à jour, Docker et préparation de l’hôte.</t>
-  </si>
-  <si>
-    <t>Architecture et schéma</t>
-  </si>
-  <si>
-    <t>Lisibilité, cohérence, zones de confiance, flux, exposition et parcours métier.</t>
-  </si>
-  <si>
-    <t>Déploiement conteneurisé</t>
-  </si>
-  <si>
-    <t>Qualité de la stack Docker Compose, structure, dépendances, volumes et reproductibilité.</t>
-  </si>
-  <si>
-    <t>Sécurité des images</t>
-  </si>
-  <si>
-    <t>Versions explicites, provenance, scan ou validation et justification des images.</t>
-  </si>
-  <si>
-    <t>Sécurité à l’exécution</t>
-  </si>
-  <si>
-    <t>Non-root, absence de privilèges injustifiés, réduction des privilèges, options de sécurité et ressources.</t>
-  </si>
-  <si>
-    <t>Segmentation réseau</t>
-  </si>
-  <si>
-    <t>Réseaux d’exposition, applicatifs et de données; exposition minimale et flux justifiés.</t>
-  </si>
-  <si>
-    <t>Intégration Drupal Commerce → n8n → Moodle</t>
-  </si>
-  <si>
-    <t>Parcours vente/paiement simulé, workflow n8n, puis attribution d’accès Moodle.</t>
-  </si>
-  <si>
-    <t>IAM et SSO</t>
-  </si>
-  <si>
-    <t>Keycloak, SSO Moodle et compréhension des flux d’authentification.</t>
-  </si>
-  <si>
-    <t>Reverse proxy et WAF</t>
-  </si>
-  <si>
-    <t>Rôle de Traefik, rôle d’OpenAppSec et centralisation de l’exposition.</t>
-  </si>
-  <si>
-    <t>Observabilité et exploitation</t>
-  </si>
-  <si>
-    <t>Usage de Portainer CE, états, journaux et diagnostic; Grafana/Loki optionnel.</t>
-  </si>
-  <si>
-    <t>Qualité des livrables</t>
-  </si>
-  <si>
-    <t>Vidéo M365 conforme, GitBook, GitHub, document Word/PPT et cohérence globale.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Résultat (%)</t>
-  </si>
-  <si>
-    <t>Appréciation</t>
-  </si>
-  <si>
-    <t>Insuffisant</t>
-  </si>
-  <si>
-    <t>Pénalités majeures à considérer</t>
-  </si>
-  <si>
-    <t>• Secrets réels committés dans GitHub.</t>
-  </si>
-  <si>
-    <t>• Conteneur applicatif en mode privilégié sans justification sérieuse.</t>
-  </si>
-  <si>
-    <t>• Exposition publique directe de PostgreSQL, Redis, n8n ou d’une interface d’administration sensible.</t>
-  </si>
-  <si>
-    <t>• Absence réelle de cloud-init malgré une revendication de VM as Code.</t>
-  </si>
-  <si>
-    <t>• Vidéo dépassant 15 min 59 s.</t>
-  </si>
-  <si>
-    <t>• Dépôt GitHub inutilisable, incomplet ou non reproductible.</t>
-  </si>
-  <si>
-    <t>Référentiel</t>
-  </si>
-  <si>
-    <t>Référentiel des niveaux de performance</t>
-  </si>
-  <si>
-    <t>Excellent</t>
-  </si>
-  <si>
-    <t>Satisfaisant</t>
-  </si>
-  <si>
-    <t>Fragile</t>
-  </si>
-  <si>
-    <t>Démonstration complète, cohérente, claire et reproductible.</t>
-  </si>
-  <si>
-    <t>Exigences principales respectées; quelques lacunes mineures.</t>
-  </si>
-  <si>
-    <t>Mise en œuvre partielle, peu démontrée ou peu justifiée.</t>
-  </si>
-  <si>
-    <t>Absent, incorrect, non démontré ou difficilement exploitable.</t>
-  </si>
-  <si>
-    <t>Consignes</t>
-  </si>
-  <si>
-    <t>Consignes de correction</t>
-  </si>
-  <si>
-    <t>Livrables à vérifier</t>
-  </si>
-  <si>
-    <t>Vidéo M365/Stream; GitBook; GitHub; document Word ou PowerPoint de 10 pages maximum, page de garde comprise.</t>
-  </si>
-  <si>
-    <t>Durée vidéo</t>
-  </si>
-  <si>
-    <t>Entre 15 min 00 s et 15 min 59 s. Toute vidéo plus longue constitue une pénalité majeure.</t>
-  </si>
-  <si>
-    <t>Scénario métier</t>
-  </si>
-  <si>
-    <t>Drupal Commerce présente une formation; un paiement fictif, sandbox ou simulé déclenche n8n; n8n attribue ou synchronise un accès dans Moodle.</t>
-  </si>
-  <si>
-    <t>Socle technique</t>
-  </si>
-  <si>
-    <t>Une VM Linux initialisée par cloud-init; stack déployée avec Docker Compose; Traefik, OpenAppSec, Drupal Commerce, Moodle, Keycloak, n8n, Portainer CE et services de données pertinents.</t>
-  </si>
-  <si>
-    <t>Attribuer la note selon les preuves visibles dans la vidéo, le code du dépôt et la documentation. Une solution plus simple mais stable, sécurisée et expliquée vaut mieux qu’une solution ambitieuse mais non maîtrisée.</t>
-  </si>
-  <si>
-    <t>Repères sécurité</t>
-  </si>
-  <si>
-    <t>Vérifier le moindre privilège, l’absence de conteneurs privilégiés injustifiés, l’usage de versions explicites, une exposition minimale et une segmentation réseau cohérente.</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="0.0%"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
+      <name val="Calibri"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color indexed="8"/>
       <sz val="14"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color indexed="11"/>
+      <sz val="12"/>
       <u val="single"/>
-      <sz val="12"/>
-      <color indexed="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color indexed="8"/>
       <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color indexed="12"/>
       <sz val="16"/>
-      <color indexed="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color indexed="12"/>
       <sz val="11"/>
-      <color indexed="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
     </font>
   </fonts>
   <fills count="10">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -518,7 +126,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -836,211 +444,293 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="16"/>
+      </right>
+      <top style="thin">
+        <color indexed="16"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="16"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="16"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="16"/>
+      </right>
+      <top style="thin">
+        <color indexed="16"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="16"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="14"/>
+      </left>
+      <right style="thin">
+        <color indexed="14"/>
+      </right>
+      <top style="thin">
+        <color indexed="14"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="14"/>
+      </left>
+      <right style="thin">
+        <color indexed="14"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="16"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+  <cellXfs count="76">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="28" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="ff000000"/>
@@ -1068,8 +758,80 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Perplexity</author>
+  </authors>
+  <commentList>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>Perplexity:
+Entrer une note de 0 à 5.</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>Perplexity:
+Entrer une note de 0 à 5.</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>Perplexity:
+Entrer une note de 0 à 4.</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>Perplexity:
+Entrer une note de 0 à 4.</t>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="0" shapeId="0">
+      <text>
+        <t>Perplexity:
+Entrer une note de 0 à 5.</t>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0" shapeId="0">
+      <text>
+        <t>Perplexity:
+Entrer une note de 0 à 4.</t>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0" shapeId="0">
+      <text>
+        <t>Perplexity:
+Entrer une note de 0 à 4.</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>Perplexity:
+Entrer une note de 0 à 4.</t>
+      </text>
+    </comment>
+    <comment ref="C14" authorId="0" shapeId="0">
+      <text>
+        <t>Perplexity:
+Entrer une note de 0 à 2.</t>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="0" shapeId="0">
+      <text>
+        <t>Perplexity:
+Entrer une note de 0 à 2.</t>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <t>Perplexity:
+Entrer une note de 0 à 5.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2127,77 +1889,106 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B3:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="4" width="30.5547" customWidth="1"/>
+    <col width="2" customWidth="1" style="64" min="1" max="1"/>
+    <col width="30.5547" customWidth="1" style="64" min="2" max="4"/>
   </cols>
   <sheetData>
-    <row r="3" ht="50" customHeight="1">
-      <c r="B3" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="C3"/>
-      <c r="D3"/>
+    <row r="3" ht="50" customHeight="1" s="64">
+      <c r="B3" s="65" t="inlineStr">
+        <is>
+          <t>This document was exported from Numbers.  Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>3</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Numbers Sheet Name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Numbers Table Name</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Excel Worksheet Name</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="s" s="3">
-        <v>4</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="4"/>
-      <c r="C10" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s" s="5">
-        <v>4</v>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="s" s="3">
-        <v>49</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Référentiel</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="4"/>
-      <c r="C12" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s" s="5">
-        <v>49</v>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Référentiel</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="s" s="3">
-        <v>58</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Consignes</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="4"/>
-      <c r="C14" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="D14" t="s" s="5">
-        <v>58</v>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Consignes</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2209,648 +2000,941 @@
     <hyperlink ref="D12" location="'Référentiel'!R1C1" tooltip="" display="Référentiel"/>
     <hyperlink ref="D14" location="'Consignes'!R1C1" tooltip="" display="Consignes"/>
   </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="35" style="6" customWidth="1"/>
-    <col min="2" max="2" width="10" style="6" customWidth="1"/>
-    <col min="3" max="3" width="14" style="6" customWidth="1"/>
-    <col min="4" max="4" width="17" style="6" customWidth="1"/>
-    <col min="5" max="5" width="42" style="6" customWidth="1"/>
-    <col min="6" max="6" width="48" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="8.85156" style="6" customWidth="1"/>
+    <col width="35" customWidth="1" style="57" min="1" max="1"/>
+    <col width="10" customWidth="1" style="57" min="2" max="2"/>
+    <col width="14" customWidth="1" style="57" min="3" max="3"/>
+    <col width="17" customWidth="1" style="57" min="4" max="4"/>
+    <col width="42" customWidth="1" style="57" min="5" max="5"/>
+    <col width="48" customWidth="1" style="57" min="6" max="6"/>
+    <col width="8.851559999999999" customWidth="1" style="57" min="7" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" t="s" s="7">
-        <v>6</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="9"/>
-    </row>
-    <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" s="10"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="12"/>
-    </row>
-    <row r="3" ht="13.55" customHeight="1">
-      <c r="A3" t="s" s="13">
-        <v>7</v>
-      </c>
-      <c r="B3" s="14"/>
-      <c r="C3" t="s" s="15">
-        <v>8</v>
-      </c>
-      <c r="D3" s="14"/>
-      <c r="E3" t="s" s="15">
-        <v>9</v>
-      </c>
-      <c r="F3" s="16"/>
-    </row>
-    <row r="4" ht="14.05" customHeight="1">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20"/>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" t="s" s="21">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s" s="21">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s" s="21">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s" s="21">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s" s="21">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" t="s" s="22">
-        <v>16</v>
-      </c>
-      <c r="B6" s="23">
+    <row r="1" ht="28" customHeight="1" s="64">
+      <c r="A1" s="66" t="inlineStr">
+        <is>
+          <t>Grille de correction — plateforme pédagogique conteneurisée</t>
+        </is>
+      </c>
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="68" t="n"/>
+    </row>
+    <row r="2" ht="13.55" customHeight="1" s="64">
+      <c r="A2" s="10" t="n"/>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="12" t="n"/>
+    </row>
+    <row r="3" ht="13.55" customHeight="1" s="64">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Équipe</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Correcteur</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="n"/>
+    </row>
+    <row r="4" ht="14.05" customHeight="1" s="64">
+      <c r="A4" s="17" t="n"/>
+      <c r="B4" s="18" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="20" t="n"/>
+    </row>
+    <row r="5" ht="34" customHeight="1" s="64">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Critère</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>Maximum</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Note attribuée</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Niveau</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>Commentaires / preuves observées</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>Indicateurs clés</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1" s="64">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>VM as Code avec cloud-init</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="26"/>
-      <c r="F6" t="s" s="22">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" t="s" s="22">
-        <v>18</v>
-      </c>
-      <c r="B7" s="23">
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="56" t="n"/>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Présence d'un vrai fichier cloud-init, utilité réelle, automatisation de l'utilisateur, SSH, mises à jour, Docker, pare-feu hôte, préparation de l'hôte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1" s="64">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Architecture et schéma</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="26"/>
-      <c r="F7" t="s" s="22">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" t="s" s="22">
-        <v>20</v>
-      </c>
-      <c r="B8" s="23">
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="25" t="n"/>
+      <c r="E7" s="56" t="n"/>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>Lisibilité, cohérence, zones de confiance, flux, exposition, parcours métier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1" s="64">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Déploiement conteneurisé</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="25" t="n"/>
+      <c r="E8" s="56" t="n"/>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>Qualité de la stack Docker Compose, structure, dépendances, reproductibilité (bonus qualitatif si Opencast ou Redis intégrés).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1" s="64">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Sécurité des images</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="25" t="n"/>
+      <c r="E9" s="56" t="n"/>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>Versions explicites, choix d'images, scan local/hors-ligne (ex. Trivy, Grype) sans dépendance à un service cloud, provenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1" s="64">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Sécurité à l'exécution</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="25" t="n"/>
+      <c r="E10" s="56" t="n"/>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>Non-root, absence de mode privilégié, réduction des privilèges, options de sécurité, montages prudents, ressources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1" s="64">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Segmentation réseau</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="56" t="n"/>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>Réseaux d'exposition, applicatifs, données, exposition minimale, flux justifiés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1" s="64">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Intégration Drupal Commerce → n8n → Moodle</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="56" t="n"/>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>Cohérence du parcours métier, vente, automatisation, attribution d'accès, démonstration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1" s="64">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>IAM et SSO</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="56" t="n"/>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>Keycloak, SSO Moodle, compréhension des flux d'authentification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1" s="64">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Reverse proxy</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="56" t="n"/>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>Rôle de Traefik, centralisation de l'exposition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1" s="64">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Observabilité et exploitation</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="56" t="n"/>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>Usage de Portainer CE, états des conteneurs, journaux, diagnostic, éventuellement Grafana/Loki.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1" s="64">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Qualité des livrables</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
-      <c r="F8" t="s" s="22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" t="s" s="22">
-        <v>22</v>
-      </c>
-      <c r="B9" s="23">
-        <v>4</v>
-      </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
-      <c r="F9" t="s" s="22">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" t="s" s="22">
-        <v>24</v>
-      </c>
-      <c r="B10" s="23">
-        <v>5</v>
-      </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="26"/>
-      <c r="F10" t="s" s="22">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" t="s" s="22">
-        <v>26</v>
-      </c>
-      <c r="B11" s="23">
-        <v>4</v>
-      </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="26"/>
-      <c r="F11" t="s" s="22">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" t="s" s="22">
-        <v>28</v>
-      </c>
-      <c r="B12" s="23">
-        <v>4</v>
-      </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
-      <c r="F12" t="s" s="22">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" t="s" s="22">
-        <v>30</v>
-      </c>
-      <c r="B13" s="23">
-        <v>4</v>
-      </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
-      <c r="F13" t="s" s="22">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" t="s" s="22">
-        <v>32</v>
-      </c>
-      <c r="B14" s="23">
-        <v>2</v>
-      </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="26"/>
-      <c r="F14" t="s" s="22">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" t="s" s="22">
-        <v>34</v>
-      </c>
-      <c r="B15" s="23">
-        <v>2</v>
-      </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="26"/>
-      <c r="F15" t="s" s="22">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" t="s" s="27">
-        <v>36</v>
-      </c>
-      <c r="B16" s="28">
-        <v>5</v>
-      </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="31"/>
-      <c r="F16" t="s" s="27">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" ht="14.55" customHeight="1">
-      <c r="A17" t="s" s="32">
-        <v>38</v>
-      </c>
-      <c r="B17" s="33" cm="1">
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="30" t="n"/>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="27" t="inlineStr">
+        <is>
+          <t>Vidéo M365 conforme, GitBook, GitHub, document Word/PPT, cohérence globale, traçabilité des contributions individuelles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="14.55" customHeight="1" s="64">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B17" s="33">
         <f t="array" ref="B17">SUM(B6:B16)</f>
-        <v>44</v>
-      </c>
-      <c r="C17" s="34" cm="1">
+        <v/>
+      </c>
+      <c r="C17" s="34">
         <f t="array" ref="C17">SUM(C6:C16)</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="36"/>
-    </row>
-    <row r="18" ht="14.05" customHeight="1">
-      <c r="A18" s="37"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="40"/>
-    </row>
-    <row r="19" ht="13.55" customHeight="1">
-      <c r="A19" t="s" s="41">
-        <v>39</v>
-      </c>
-      <c r="B19" s="42" cm="1">
+        <v/>
+      </c>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="36" t="n"/>
+    </row>
+    <row r="18" ht="14.05" customHeight="1" s="64">
+      <c r="A18" s="37" t="n"/>
+      <c r="B18" s="38" t="n"/>
+      <c r="C18" s="39" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="38" t="n"/>
+      <c r="F18" s="40" t="n"/>
+    </row>
+    <row r="19" ht="13.55" customHeight="1" s="64">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>Résultat (%)</t>
+        </is>
+      </c>
+      <c r="B19" s="69">
         <f t="array" ref="B19">C17/B17</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="11"/>
-      <c r="D19" t="s" s="43">
-        <v>40</v>
-      </c>
-      <c r="E19" t="str" s="44" cm="1">
+        <v/>
+      </c>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>Appréciation</t>
+        </is>
+      </c>
+      <c r="E19" s="44">
         <f t="array" ref="E19">IF(C17&gt;=36,"Excellent",IF(C17&gt;=28,"Satisfaisant",IF(C17&gt;=20,"Fragile","Insuffisant")))</f>
-        <v>Insuffisant</v>
-      </c>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" ht="13.55" customHeight="1">
-      <c r="A20" t="s" s="45">
-        <v>42</v>
-      </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="12"/>
-    </row>
-    <row r="21" ht="13.55" customHeight="1">
-      <c r="A21" t="s" s="46">
-        <v>43</v>
-      </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" ht="13.55" customHeight="1">
-      <c r="A22" t="s" s="46">
-        <v>44</v>
-      </c>
-      <c r="B22" s="47"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" ht="13.55" customHeight="1">
-      <c r="A23" t="s" s="46">
-        <v>45</v>
-      </c>
-      <c r="B23" s="47"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-    </row>
-    <row r="24" ht="13.55" customHeight="1">
-      <c r="A24" t="s" s="46">
-        <v>46</v>
-      </c>
-      <c r="B24" s="47"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="25" ht="13.55" customHeight="1">
-      <c r="A25" t="s" s="46">
-        <v>47</v>
-      </c>
-      <c r="B25" s="47"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="12"/>
-    </row>
-    <row r="26" ht="13.55" customHeight="1">
-      <c r="A26" t="s" s="46">
-        <v>48</v>
-      </c>
-      <c r="B26" s="48"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="50"/>
+        <v/>
+      </c>
+      <c r="F19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="13.55" customHeight="1" s="64">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Bonus — WAF (OpenAppSec)</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>+2 (hors total)</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="56" t="n"/>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>Rôle d'OpenAppSec en mode local (sans compte cloud tiers), optionnel et non requis; +2 si fonctionnel et bien expliqué, +1 si partiel, 0 si absent ou en mode cloud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="13.55" customHeight="1" s="64">
+      <c r="A21" s="70" t="inlineStr">
+        <is>
+          <t>Pénalités majeures à considérer</t>
+        </is>
+      </c>
+      <c r="B21" s="71" t="n"/>
+      <c r="C21" s="71" t="n"/>
+      <c r="D21" s="71" t="n"/>
+      <c r="E21" s="71" t="n"/>
+      <c r="F21" s="72" t="n"/>
+    </row>
+    <row r="22" ht="13.55" customHeight="1" s="64">
+      <c r="A22" s="46" t="inlineStr">
+        <is>
+          <t>• Secrets réels committés dans GitHub.</t>
+        </is>
+      </c>
+      <c r="B22" s="73" t="n"/>
+      <c r="C22" s="73" t="n"/>
+      <c r="D22" s="73" t="n"/>
+      <c r="E22" s="73" t="n"/>
+      <c r="F22" s="74" t="n"/>
+    </row>
+    <row r="23" ht="13.55" customHeight="1" s="64">
+      <c r="A23" s="46" t="inlineStr">
+        <is>
+          <t>• Conteneur applicatif en mode privilégié sans justification sérieuse.</t>
+        </is>
+      </c>
+      <c r="B23" s="73" t="n"/>
+      <c r="C23" s="73" t="n"/>
+      <c r="D23" s="73" t="n"/>
+      <c r="E23" s="73" t="n"/>
+      <c r="F23" s="74" t="n"/>
+    </row>
+    <row r="24" ht="13.55" customHeight="1" s="64">
+      <c r="A24" s="46" t="inlineStr">
+        <is>
+          <t>• Exposition publique directe de PostgreSQL, Redis, n8n ou d’une interface d’administration sensible.</t>
+        </is>
+      </c>
+      <c r="B24" s="73" t="n"/>
+      <c r="C24" s="73" t="n"/>
+      <c r="D24" s="73" t="n"/>
+      <c r="E24" s="73" t="n"/>
+      <c r="F24" s="74" t="n"/>
+    </row>
+    <row r="25" ht="13.55" customHeight="1" s="64">
+      <c r="A25" s="46" t="inlineStr">
+        <is>
+          <t>• Absence réelle de cloud-init malgré une revendication de VM as Code.</t>
+        </is>
+      </c>
+      <c r="B25" s="73" t="n"/>
+      <c r="C25" s="73" t="n"/>
+      <c r="D25" s="73" t="n"/>
+      <c r="E25" s="73" t="n"/>
+      <c r="F25" s="74" t="n"/>
+    </row>
+    <row r="26" ht="13.55" customHeight="1" s="64">
+      <c r="A26" s="46" t="inlineStr">
+        <is>
+          <t>• Vidéo dépassant 15 min 59 s.</t>
+        </is>
+      </c>
+      <c r="B26" s="73" t="n"/>
+      <c r="C26" s="73" t="n"/>
+      <c r="D26" s="73" t="n"/>
+      <c r="E26" s="73" t="n"/>
+      <c r="F26" s="74" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>• Dépôt GitHub inutilisable, incomplet ou non reproductible.</t>
+        </is>
+      </c>
+      <c r="B27" s="73" t="n"/>
+      <c r="C27" s="73" t="n"/>
+      <c r="D27" s="73" t="n"/>
+      <c r="E27" s="73" t="n"/>
+      <c r="F27" s="74" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="46" t="inlineStr">
+        <is>
+          <t>• Incapacité d'expliquer les réseaux, les flux ou les dépendances (pénalité sur les critères concernés).</t>
+        </is>
+      </c>
+      <c r="B28" s="73" t="n"/>
+      <c r="C28" s="73" t="n"/>
+      <c r="D28" s="73" t="n"/>
+      <c r="E28" s="73" t="n"/>
+      <c r="F28" s="74" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="46" t="inlineStr">
+        <is>
+          <t>• Contributions individuelles non identifiables (-1 à -2 points sur Qualité des livrables).</t>
+        </is>
+      </c>
+      <c r="B29" s="73" t="n"/>
+      <c r="C29" s="73" t="n"/>
+      <c r="D29" s="73" t="n"/>
+      <c r="E29" s="73" t="n"/>
+      <c r="F29" s="74" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D16">
+    <dataValidation sqref="D6:D16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Excellent,Satisfaisant,Fragile,Insuffisant"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
+  <pageSetup orientation="landscape" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="37" style="51" customWidth="1"/>
-    <col min="2" max="5" width="35" style="51" customWidth="1"/>
-    <col min="6" max="6" width="10" style="51" customWidth="1"/>
-    <col min="7" max="16384" width="8.85156" style="51" customWidth="1"/>
+    <col width="37" customWidth="1" style="57" min="1" max="1"/>
+    <col width="35" customWidth="1" style="57" min="2" max="5"/>
+    <col width="10" customWidth="1" style="57" min="6" max="6"/>
+    <col width="8.851559999999999" customWidth="1" style="57" min="7" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.45" customHeight="1">
-      <c r="A1" t="s" s="52">
-        <v>50</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="9"/>
-    </row>
-    <row r="2" ht="14.05" customHeight="1">
-      <c r="A2" s="17"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="53"/>
-    </row>
-    <row r="3" ht="14.05" customHeight="1">
-      <c r="A3" t="s" s="54">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s" s="54">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s" s="54">
-        <v>52</v>
-      </c>
-      <c r="D3" t="s" s="54">
-        <v>53</v>
-      </c>
-      <c r="E3" t="s" s="54">
-        <v>41</v>
-      </c>
-      <c r="F3" t="s" s="54">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" ht="58" customHeight="1">
-      <c r="A4" t="s" s="22">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s" s="55">
-        <v>54</v>
-      </c>
-      <c r="C4" t="s" s="55">
-        <v>55</v>
-      </c>
-      <c r="D4" t="s" s="55">
-        <v>56</v>
-      </c>
-      <c r="E4" t="s" s="55">
-        <v>57</v>
-      </c>
-      <c r="F4" s="56">
+    <row r="1" ht="19.45" customHeight="1" s="64">
+      <c r="A1" s="75" t="inlineStr">
+        <is>
+          <t>Référentiel des niveaux de performance</t>
+        </is>
+      </c>
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="68" t="n"/>
+    </row>
+    <row r="2" ht="14.05" customHeight="1" s="64">
+      <c r="A2" s="17" t="n"/>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="53" t="n"/>
+    </row>
+    <row r="3" ht="14.05" customHeight="1" s="64">
+      <c r="A3" s="54" t="inlineStr">
+        <is>
+          <t>Critère</t>
+        </is>
+      </c>
+      <c r="B3" s="54" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+      <c r="C3" s="54" t="inlineStr">
+        <is>
+          <t>Satisfaisant</t>
+        </is>
+      </c>
+      <c r="D3" s="54" t="inlineStr">
+        <is>
+          <t>Fragile</t>
+        </is>
+      </c>
+      <c r="E3" s="54" t="inlineStr">
+        <is>
+          <t>Insuffisant</t>
+        </is>
+      </c>
+      <c r="F3" s="54" t="inlineStr">
+        <is>
+          <t>Maximum</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1" s="64">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>VM as Code avec cloud-init</t>
+        </is>
+      </c>
+      <c r="B4" s="55" t="inlineStr">
+        <is>
+          <t>Cloud-init complet, clair, reproductible, réellement utile au déploiement.</t>
+        </is>
+      </c>
+      <c r="C4" s="55" t="inlineStr">
+        <is>
+          <t>Cloud-init pertinent mais partiellement incomplet ou peu expliqué.</t>
+        </is>
+      </c>
+      <c r="D4" s="55" t="inlineStr">
+        <is>
+          <t>Cloud-init minimal, partiel ou surtout décoratif.</t>
+        </is>
+      </c>
+      <c r="E4" s="55" t="inlineStr">
+        <is>
+          <t>Absence de vrai cloud-init ou usage non démontré.</t>
+        </is>
+      </c>
+      <c r="F4" s="56" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" t="s" s="22">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s" s="55">
-        <v>54</v>
-      </c>
-      <c r="C5" t="s" s="55">
-        <v>55</v>
-      </c>
-      <c r="D5" t="s" s="55">
-        <v>56</v>
-      </c>
-      <c r="E5" t="s" s="55">
-        <v>57</v>
-      </c>
-      <c r="F5" s="56">
+    <row r="5" ht="58" customHeight="1" s="64">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Architecture et schéma</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Schéma clair, complet, juste et aligné avec le déploiement réel.</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>Schéma généralement bon, avec quelques oublis mineurs.</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>Schéma partiel, ambigu ou difficile à relier à la solution.</t>
+        </is>
+      </c>
+      <c r="E5" s="55" t="inlineStr">
+        <is>
+          <t>Schéma absent ou incorrect.</t>
+        </is>
+      </c>
+      <c r="F5" s="56" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" t="s" s="22">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s" s="55">
-        <v>54</v>
-      </c>
-      <c r="C6" t="s" s="55">
-        <v>55</v>
-      </c>
-      <c r="D6" t="s" s="55">
-        <v>56</v>
-      </c>
-      <c r="E6" t="s" s="55">
-        <v>57</v>
-      </c>
-      <c r="F6" s="56">
+    <row r="6" ht="58" customHeight="1" s="64">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Déploiement conteneurisé</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>Stack fonctionnelle, propre, stable et bien structurée.</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>Stack presque complète avec quelques imprécisions mineures.</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="inlineStr">
+        <is>
+          <t>Stack partiellement fonctionnelle ou difficile à reproduire.</t>
+        </is>
+      </c>
+      <c r="E6" s="55" t="inlineStr">
+        <is>
+          <t>Solution non déployable ou incohérente.</t>
+        </is>
+      </c>
+      <c r="F6" s="56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1" s="64">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Sécurité des images</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>Images bien choisies, versions explicites, scan ou justification convaincante.</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>Bonnes pratiques visibles mais démonstration incomplète.</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="inlineStr">
+        <is>
+          <t>Peu d'éléments de sécurité ou choix peu justifiés.</t>
+        </is>
+      </c>
+      <c r="E7" s="55" t="inlineStr">
+        <is>
+          <t>Aucune preuve sérieuse de réflexion sur les images.</t>
+        </is>
+      </c>
+      <c r="F7" s="56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1" s="64">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Sécurité à l'exécution</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>Bonnes pratiques visibles, expliquées et majoritairement appliquées.</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>Plusieurs contrôles corrects, quelques écarts justifiés.</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t>Sécurité partielle ou surtout déclarative.</t>
+        </is>
+      </c>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>Presque aucun durcissement réel.</t>
+        </is>
+      </c>
+      <c r="F8" s="56" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1" s="64">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Segmentation réseau</t>
+        </is>
+      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>Segmentation claire, bien pensée et bien expliquée.</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>Segmentation présente mais perfectible.</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="inlineStr">
+        <is>
+          <t>Segmentation minimale ou peu cohérente.</t>
+        </is>
+      </c>
+      <c r="E9" s="55" t="inlineStr">
+        <is>
+          <t>Réseau plat ou services sensibles exposés inutilement.</t>
+        </is>
+      </c>
+      <c r="F9" s="56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1" s="64">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Intégration Drupal Commerce → n8n → Moodle</t>
+        </is>
+      </c>
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>Flux cohérent, démontré, compréhensible et bien documenté.</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>Flux présent mais partiellement simulé ou incomplet.</t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="inlineStr">
+        <is>
+          <t>Logique annoncée mais peu démontrée.</t>
+        </is>
+      </c>
+      <c r="E10" s="55" t="inlineStr">
+        <is>
+          <t>Aucune intégration crédible entre les composants.</t>
+        </is>
+      </c>
+      <c r="F10" s="56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1" s="64">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>IAM et SSO</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>SSO fonctionnel, bien démontré et bien expliqué.</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>SSO partiellement fonctionnel ou démonstration incomplète.</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>Configuration présente mais peu convaincante.</t>
+        </is>
+      </c>
+      <c r="E11" s="55" t="inlineStr">
+        <is>
+          <t>Absence de mise en œuvre réelle.</t>
+        </is>
+      </c>
+      <c r="F11" s="56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1" s="64">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Reverse proxy</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>Proxy intégré et correctement expliqué.</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>Présence partielle ou démonstration limitée.</t>
+        </is>
+      </c>
+      <c r="D12" s="55" t="inlineStr">
+        <is>
+          <t>Compréhension faible, intégration incomplète.</t>
+        </is>
+      </c>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>Absence ou incompréhension manifeste.</t>
+        </is>
+      </c>
+      <c r="F12" s="56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1" s="64">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Observabilité et exploitation</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>Portainer CE opérationnel et utilisé intelligemment; diagnostic crédible montré.</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>Portainer présent et exploité partiellement.</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="inlineStr">
+        <is>
+          <t>Portainer peu exploité ou démonstration faible.</t>
+        </is>
+      </c>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>Aucun usage pédagogique réel de l'observabilité.</t>
+        </is>
+      </c>
+      <c r="F13" s="56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1" s="64">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Qualité des livrables</t>
+        </is>
+      </c>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>Tous les livrables sont complets, cohérents, clairs et professionnels.</t>
+        </is>
+      </c>
+      <c r="C14" s="55" t="inlineStr">
+        <is>
+          <t>Très bons livrables avec quelques défauts mineurs.</t>
+        </is>
+      </c>
+      <c r="D14" s="55" t="inlineStr">
+        <is>
+          <t>Livrables présents mais inégaux ou difficiles à exploiter.</t>
+        </is>
+      </c>
+      <c r="E14" s="55" t="inlineStr">
+        <is>
+          <t>Plusieurs livrables absents, non accessibles ou de faible qualité.</t>
+        </is>
+      </c>
+      <c r="F14" s="56" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" t="s" s="22">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s" s="55">
-        <v>54</v>
-      </c>
-      <c r="C7" t="s" s="55">
-        <v>55</v>
-      </c>
-      <c r="D7" t="s" s="55">
-        <v>56</v>
-      </c>
-      <c r="E7" t="s" s="55">
-        <v>57</v>
-      </c>
-      <c r="F7" s="56">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" t="s" s="22">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s" s="55">
-        <v>54</v>
-      </c>
-      <c r="C8" t="s" s="55">
-        <v>55</v>
-      </c>
-      <c r="D8" t="s" s="55">
-        <v>56</v>
-      </c>
-      <c r="E8" t="s" s="55">
-        <v>57</v>
-      </c>
-      <c r="F8" s="56">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" t="s" s="22">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s" s="55">
-        <v>54</v>
-      </c>
-      <c r="C9" t="s" s="55">
-        <v>55</v>
-      </c>
-      <c r="D9" t="s" s="55">
-        <v>56</v>
-      </c>
-      <c r="E9" t="s" s="55">
-        <v>57</v>
-      </c>
-      <c r="F9" s="56">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" t="s" s="22">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s" s="55">
-        <v>54</v>
-      </c>
-      <c r="C10" t="s" s="55">
-        <v>55</v>
-      </c>
-      <c r="D10" t="s" s="55">
-        <v>56</v>
-      </c>
-      <c r="E10" t="s" s="55">
-        <v>57</v>
-      </c>
-      <c r="F10" s="56">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" t="s" s="22">
-        <v>30</v>
-      </c>
-      <c r="B11" t="s" s="55">
-        <v>54</v>
-      </c>
-      <c r="C11" t="s" s="55">
-        <v>55</v>
-      </c>
-      <c r="D11" t="s" s="55">
-        <v>56</v>
-      </c>
-      <c r="E11" t="s" s="55">
-        <v>57</v>
-      </c>
-      <c r="F11" s="56">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" t="s" s="22">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s" s="55">
-        <v>54</v>
-      </c>
-      <c r="C12" t="s" s="55">
-        <v>55</v>
-      </c>
-      <c r="D12" t="s" s="55">
-        <v>56</v>
-      </c>
-      <c r="E12" t="s" s="55">
-        <v>57</v>
-      </c>
-      <c r="F12" s="56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" t="s" s="22">
-        <v>34</v>
-      </c>
-      <c r="B13" t="s" s="55">
-        <v>54</v>
-      </c>
-      <c r="C13" t="s" s="55">
-        <v>55</v>
-      </c>
-      <c r="D13" t="s" s="55">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s" s="55">
-        <v>57</v>
-      </c>
-      <c r="F13" s="56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" t="s" s="22">
-        <v>36</v>
-      </c>
-      <c r="B14" t="s" s="55">
-        <v>54</v>
-      </c>
-      <c r="C14" t="s" s="55">
-        <v>55</v>
-      </c>
-      <c r="D14" t="s" s="55">
-        <v>56</v>
-      </c>
-      <c r="E14" t="s" s="55">
-        <v>57</v>
-      </c>
-      <c r="F14" s="56">
-        <v>5</v>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Bonus — WAF (OpenAppSec)</t>
+        </is>
+      </c>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>WAF fonctionnel, en mode local, bien intégré et expliqué (+2).</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t>WAF présent mais partiel ou peu expliqué (+1).</t>
+        </is>
+      </c>
+      <c r="D15" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>Absent ou en mode cloud, aucun bonus (0).</t>
+        </is>
+      </c>
+      <c r="F15" s="56" t="inlineStr">
+        <is>
+          <t>+2 (hors total)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2858,123 +2942,155 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
+  <pageSetup orientation="landscape" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="25" style="57" customWidth="1"/>
-    <col min="2" max="2" width="42" style="57" customWidth="1"/>
-    <col min="3" max="4" width="25" style="57" customWidth="1"/>
-    <col min="5" max="5" width="8.85156" style="57" customWidth="1"/>
-    <col min="6" max="16384" width="8.85156" style="57" customWidth="1"/>
+    <col width="25" customWidth="1" style="57" min="1" max="1"/>
+    <col width="42" customWidth="1" style="57" min="2" max="2"/>
+    <col width="25" customWidth="1" style="57" min="3" max="4"/>
+    <col width="8.851559999999999" customWidth="1" style="57" min="5" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="57" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.45" customHeight="1">
-      <c r="A1" t="s" s="52">
-        <v>59</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9"/>
-    </row>
-    <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" s="58"/>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="12"/>
-    </row>
-    <row r="3" ht="52" customHeight="1">
-      <c r="A3" t="s" s="60">
-        <v>60</v>
-      </c>
-      <c r="B3" t="s" s="55">
-        <v>61</v>
-      </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="61"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" t="s" s="60">
-        <v>62</v>
-      </c>
-      <c r="B4" t="s" s="55">
-        <v>63</v>
-      </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="61"/>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" t="s" s="60">
-        <v>64</v>
-      </c>
-      <c r="B5" t="s" s="55">
-        <v>65</v>
-      </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="61"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" t="s" s="60">
-        <v>66</v>
-      </c>
-      <c r="B6" t="s" s="55">
-        <v>67</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="61"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" t="s" s="60">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s" s="55">
-        <v>68</v>
-      </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="61"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" t="s" s="60">
-        <v>69</v>
-      </c>
-      <c r="B8" t="s" s="55">
-        <v>70</v>
-      </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="61"/>
-    </row>
-    <row r="9" ht="13.55" customHeight="1">
-      <c r="A9" s="62"/>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="12"/>
-    </row>
-    <row r="10" ht="13.55" customHeight="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="50"/>
+    <row r="1" ht="19.45" customHeight="1" s="64">
+      <c r="A1" s="52" t="inlineStr">
+        <is>
+          <t>Consignes de correction</t>
+        </is>
+      </c>
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="13.55" customHeight="1" s="64">
+      <c r="A2" s="58" t="n"/>
+      <c r="B2" s="59" t="n"/>
+      <c r="C2" s="59" t="n"/>
+      <c r="D2" s="59" t="n"/>
+      <c r="E2" s="12" t="n"/>
+    </row>
+    <row r="3" ht="52" customHeight="1" s="64">
+      <c r="A3" s="60" t="inlineStr">
+        <is>
+          <t>Livrables à vérifier</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t>Vidéo M365/Stream; GitBook; GitHub; document Word ou PowerPoint de 10 pages maximum, page de garde comprise.</t>
+        </is>
+      </c>
+      <c r="C3" s="73" t="n"/>
+      <c r="D3" s="74" t="n"/>
+      <c r="E3" s="61" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1" s="64">
+      <c r="A4" s="60" t="inlineStr">
+        <is>
+          <t>Durée vidéo</t>
+        </is>
+      </c>
+      <c r="B4" s="55" t="inlineStr">
+        <is>
+          <t>Durée maximale : 15 min 59 s, sans durée minimale exigée. Toute vidéo plus longue constitue une pénalité majeure.</t>
+        </is>
+      </c>
+      <c r="C4" s="73" t="n"/>
+      <c r="D4" s="74" t="n"/>
+      <c r="E4" s="61" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1" s="64">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>Scénario métier</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Drupal Commerce présente une formation; un paiement fictif, sandbox ou simulé déclenche n8n; n8n attribue ou synchronise un accès dans Moodle.</t>
+        </is>
+      </c>
+      <c r="C5" s="73" t="n"/>
+      <c r="D5" s="74" t="n"/>
+      <c r="E5" s="61" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1" s="64">
+      <c r="A6" s="60" t="inlineStr">
+        <is>
+          <t>Socle technique</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>Une VM Linux initialisée par cloud-init; stack déployée avec Docker Compose; Traefik, Drupal Commerce, Moodle, Keycloak, n8n, Portainer CE et services de données pertinents; OpenAppSec (WAF) est un bonus optionnel, non requis.</t>
+        </is>
+      </c>
+      <c r="C6" s="73" t="n"/>
+      <c r="D6" s="74" t="n"/>
+      <c r="E6" s="61" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1" s="64">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>Attribuer la note selon les preuves visibles dans la vidéo, le code du dépôt et la documentation. Une solution plus simple mais stable, sécurisée et expliquée vaut mieux qu’une solution ambitieuse mais non maîtrisée.</t>
+        </is>
+      </c>
+      <c r="C7" s="73" t="n"/>
+      <c r="D7" s="74" t="n"/>
+      <c r="E7" s="61" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1" s="64">
+      <c r="A8" s="60" t="inlineStr">
+        <is>
+          <t>Repères sécurité</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>Vérifier le moindre privilège, l’absence de conteneurs privilégiés injustifiés, l’usage de versions explicites, une exposition minimale et une segmentation réseau cohérente.</t>
+        </is>
+      </c>
+      <c r="C8" s="73" t="n"/>
+      <c r="D8" s="74" t="n"/>
+      <c r="E8" s="61" t="n"/>
+    </row>
+    <row r="9" ht="13.55" customHeight="1" s="64">
+      <c r="A9" s="62" t="n"/>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="12" t="n"/>
+    </row>
+    <row r="10" ht="13.55" customHeight="1" s="64">
+      <c r="A10" s="63" t="n"/>
+      <c r="B10" s="49" t="n"/>
+      <c r="C10" s="49" t="n"/>
+      <c r="D10" s="49" t="n"/>
+      <c r="E10" s="50" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2987,9 +3103,14 @@
     <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
+  <pageSetup orientation="landscape" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>